--- a/FPPN_Plan_de_travail_Actuariat_20261023.xlsx
+++ b/FPPN_Plan_de_travail_Actuariat_20261023.xlsx
@@ -1305,7 +1305,7 @@
       <c r="E9" s="66" t="n"/>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>PBC pointée au 23/10/2026 (FPPN_PBC_complete_pointee_20261023.xlsx) : 90 items après fusion des doublons, dont 6 reçus, 39 partiellement reçus et 45 non reçus. Questions et documents à transmettre (FPPN_Demandes_au_FPPN_20261023.xlsx : 26 questions, 84 documents). Reste : relances.</t>
+          <t>PBC pointée au 23/10/2026 (FPPN_PBC_complete_pointee_20261023.xlsx) : 90 items après fusion des doublons, dont 6 reçus, 41 partiellement reçus et 43 non reçus. Questions et documents à transmettre (FPPN_Demandes_au_FPPN_20261023.xlsx : 26 questions, 84 documents). Reste : relances.</t>
         </is>
       </c>
       <c r="G9" s="23" t="n">
@@ -1357,7 +1357,7 @@
       <c r="E10" s="66" t="n"/>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 24 à 27 (cadre juridique, statuts et règlement intérieur, garanties et produits). Versions des statuts antérieures à 2023 non reçues. Item PBC attendu : 1.</t>
+          <t>Rapport du 23/10/2026, diapositives 25 à 28 (cadre juridique, statuts et règlement intérieur, garanties et produits). Versions des statuts antérieures à 2023 non reçues. Item PBC attendu : 1.</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -1461,7 +1461,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Tables retenues (rapport du 23/10/2026, diapositives 205 à 211). SMIG de 75 000 FCFA (décret n° 2022-986 du 21/12/2022) appliqué au plafond de l'indemnité de départ (diapositive 133). Rendements lus dans les grands livres (diapositive 153). Reste : âge de départ du personnel et hypothèses de projection (phase 7). Items PBC attendus : 13, 78.</t>
+          <t>Tables retenues (rapport du 23/10/2026, diapositives 210 à 216). SMIG de 75 000 FCFA (décret n° 2022-986 du 21/12/2022) appliqué au plafond de l'indemnité de départ (diapositive 134). Rendements lus dans les grands livres (diapositive 154). Reste : âge de départ du personnel et hypothèses de projection (phase 7). Items PBC attendus : 13, 78.</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Extraction FPPN_extraction_20261018_1939.zip : 4 287 fichiers, journal journal_fichiers.csv. Envois du 22/10/2026 inventoriés. Fichiers vides ou endommagés recensés (rapport du 23/10/2026, diapositive 44).</t>
+          <t>Extraction FPPN_extraction_20261018_1939.zip : 4 287 fichiers, journal journal_fichiers.csv. Envois du 22/10/2026 inventoriés. Fichiers vides ou endommagés recensés (rapport du 23/10/2026, diapositive 45).</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -1614,7 +1614,7 @@
       <c r="E15" s="66" t="n"/>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 37 à 45 (contrôles, qualité des bases variable par variable). Vérification indépendante des chiffres (FPPN_Verification_coherence_20261023.xlsx) : 506 feuilles de précomptes, 43 102 485 135 FCFA, 7 balances identiques.</t>
+          <t>Rapport du 23/10/2026, diapositives 38 à 46 (contrôles, qualité des bases variable par variable). Vérification indépendante des chiffres (FPPN_Verification_coherence_20261023.xlsx) : 506 feuilles de précomptes, 43 102 485 135 FCFA, 7 balances identiques.</t>
         </is>
       </c>
       <c r="G15" s="23" t="n">
@@ -1666,7 +1666,7 @@
       <c r="E16" s="66" t="n"/>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 42 et 43 (rapprochement aller et retour, écarts du PEP) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglet 1_aller_retour.</t>
+          <t>Rapport du 23/10/2026, diapositives 43 et 44 (rapprochement aller et retour, écarts du PEP) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglet 1_aller_retour.</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -1718,7 +1718,7 @@
       <c r="E17" s="66" t="n"/>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>Couverture mesurée de janvier 2020 à août 2026 (rapport du 23/10/2026, diapositive 39). Restent vides : fichiers maladie 936 et décès 8Z6 de décembre 2024. Fichier retour 9X4 de décembre 2024 manquant (diapositive 44). Items PBC attendus : 38, 39, 40.</t>
+          <t>Couverture mesurée de janvier 2020 à août 2026 (rapport du 23/10/2026, diapositive 40). Restent vides : fichiers maladie 936 et décès 8Z6 de décembre 2024. Fichier retour 9X4 de décembre 2024 manquant (diapositive 45). Items PBC attendus : 38, 39, 40.</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
@@ -1770,7 +1770,7 @@
       <c r="E18" s="66" t="n"/>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Cotisations comptabilisées et précomptées rapprochées (rapport du 23/10/2026, diapositive 59). Contrôles croisés états financiers, effectifs et rapprochements bancaires (diapositives 47 à 49). Reste : comptes individuels d'épargne. Items PBC attendus : 9.</t>
+          <t>Cotisations comptabilisées et précomptées rapprochées (rapport du 23/10/2026, diapositive 60). Contrôles croisés états financiers, effectifs et rapprochements bancaires (diapositives 48 à 50). Reste : comptes individuels d'épargne. Items PBC attendus : 9.</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -1822,7 +1822,7 @@
       <c r="E19" s="66" t="n"/>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>Aucune base de prestations extraite du logiciel. Le journal SIN et les états décès de fin d'année servent de base provisoire (rapport du 23/10/2026, diapositives 110 à 118). Items PBC attendus : 16, 47.</t>
+          <t>Aucune base de prestations extraite du logiciel. Le journal SIN et les états décès de fin d'année servent de base provisoire (rapport du 23/10/2026, diapositives 111 à 119). Items PBC attendus : 16, 47.</t>
         </is>
       </c>
       <c r="G19" s="23" t="n">
@@ -1874,7 +1874,7 @@
       <c r="E20" s="67" t="n"/>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Note sur les anomalies de données du 19/10/2026. Vérification de cohérence du 23/10/2026 (FPPN_Verification_coherence_20261023.xlsx, onglet 1_Anomalies). Questions au FPPN (rapport du 23/10/2026, diapositives 229 et 230). À tenir à jour à chaque envoi.</t>
+          <t>Note sur les anomalies de données du 19/10/2026. Vérification de cohérence du 23/10/2026 (FPPN_Verification_coherence_20261023.xlsx, onglet 1_Anomalies). Questions au FPPN (rapport du 23/10/2026, diapositives 234 et 235). À tenir à jour à chaque envoi.</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, partie 4 (diapositives 50 à 62). Limite : dates de naissance absentes des fichiers de précomptes (diapositive 45), fichier des ayants droit non reçu. Items PBC attendus : 4, 43.</t>
+          <t>Rapport du 23/10/2026, partie 4 (diapositives 51 à 63). Limite : dates de naissance absentes des fichiers de précomptes (diapositive 46), fichier des ayants droit non reçu. Items PBC attendus : 4, 43.</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
@@ -2030,7 +2030,7 @@
       <c r="E23" s="66" t="n"/>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, partie 5 (diapositives 63 à 77) et ratios par garantie (diapositive 182) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 3_, 12_sinistralite_variantes et 28_ratios_garantie.</t>
+          <t>Rapport du 23/10/2026, partie 5 (diapositives 64 à 78) et ratios par garantie (diapositive 167) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 3_, 12_sinistralite_variantes et 28_ratios_garantie.</t>
         </is>
       </c>
       <c r="G23" s="23" t="n">
@@ -2082,7 +2082,7 @@
       <c r="E24" s="66" t="n"/>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, parties 6 à 8 (diapositives 78 à 104) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 4_, 5_ et 6_.</t>
+          <t>Rapport du 23/10/2026, parties 6 à 8 (diapositives 79 à 105) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 4_, 5_ et 6_.</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -2130,7 +2130,7 @@
       <c r="E25" s="66" t="n"/>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>Méthodes retenues chiffrées sur les documents reçus : provision maladie, allocations décès, intérêts dus sur l'épargne, provision du personnel agent par agent (rapport du 23/10/2026, diapositives 89, 114, 118 et 122 à 133). Méthodes écartées en annexe (diapositives 232 à 239).</t>
+          <t>Méthodes retenues chiffrées sur les documents reçus : provision maladie, allocations décès, intérêts dus sur l'épargne, provision du personnel agent par agent (rapport du 23/10/2026, diapositives 90, 115, 119 et 123 à 134). Méthodes écartées en annexe (diapositives 237 à 244).</t>
         </is>
       </c>
       <c r="G25" s="23" t="n">
@@ -2178,7 +2178,7 @@
       <c r="E26" s="66" t="n"/>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Calculs par âge impossibles : dates de naissance absentes (rapport du 23/10/2026, diapositive 45). Analyses en attente et méthode retenue pour chacune (diapositive 228). Items PBC attendus : 4, 16, 43, 47.</t>
+          <t>Calculs par âge impossibles : dates de naissance absentes (rapport du 23/10/2026, diapositive 46). Analyses en attente et méthode retenue pour chacune (diapositive 233). Items PBC attendus : 4, 16, 43, 47.</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -2226,7 +2226,7 @@
       <c r="E27" s="67" t="n"/>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>Conclusion établie sur les documents reçus (rapport du 23/10/2026, diapositive 134). Les analyses en attente la préciseront sans en changer le sens (diapositive 228).</t>
+          <t>Conclusion établie sur les documents reçus (rapport du 23/10/2026, diapositive 135). Les analyses en attente la préciseront sans en changer le sens (diapositive 233).</t>
         </is>
       </c>
       <c r="G27" s="23" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 105 à 109 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 12_provisions_inventaire, 12_psap_rapprochement et 8_provisions_mois.</t>
+          <t>Rapport du 23/10/2026, diapositives 106 à 110 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 12_provisions_inventaire, 12_psap_rapprochement et 8_provisions_mois.</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -2382,7 +2382,7 @@
       <c r="E30" s="66" t="n"/>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t>Provision maladie mesurée sur les factures arrivées après la clôture et provision décès sur les dossiers connus (rapport du 23/10/2026, diapositives 110 à 119). Reste : base des prestations datée et liste des dossiers non payés. Items PBC attendus : 7, 47, 48, 64.</t>
+          <t>Provision maladie mesurée sur les factures arrivées après la clôture et provision décès sur les dossiers connus (rapport du 23/10/2026, diapositives 111 à 120). Reste : base des prestations datée et liste des dossiers non payés. Items PBC attendus : 7, 47, 48, 64.</t>
         </is>
       </c>
       <c r="G30" s="23" t="n">
@@ -2434,7 +2434,7 @@
       <c r="E31" s="66" t="n"/>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Provisions maladie et obsèques identiques depuis le 01/09/2020 : comparaison avec le recalcul (rapport du 23/10/2026, diapositive 136). Boni et mali par exercice en attente des bases avec dates de survenance et de paiement. Items PBC attendus : 16, 47.</t>
+          <t>Provisions maladie et obsèques identiques depuis le 01/09/2020 : comparaison avec le recalcul (rapport du 23/10/2026, diapositive 137). Boni et mali par exercice en attente des bases avec dates de survenance et de paiement. Items PBC attendus : 16, 47.</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -2486,7 +2486,7 @@
       <c r="E32" s="66" t="n"/>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 120 à 133 (Grenier, compte GNA, provision du personnel avec et sans plafond conventionnel) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 12_grenier_tranches, 12_gna_47111106, 14b_pidr_individuel et 27_pidr_plafond. Reste : note de calcul de la provision du personnel. Items PBC attendus : 51, 72, 78.</t>
+          <t>Rapport du 23/10/2026, diapositives 121 à 134 (Grenier, compte GNA, provision du personnel avec et sans plafond conventionnel) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 12_grenier_tranches, 12_gna_47111106, 14b_pidr_individuel et 27_pidr_plafond. Reste : note de calcul de la provision du personnel. Items PBC attendus : 51, 72, 78.</t>
         </is>
       </c>
       <c r="G32" s="23" t="n">
@@ -2534,7 +2534,7 @@
       <c r="E33" s="67" t="n"/>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Conclusion établie sur les documents reçus (rapport du 23/10/2026, diapositives 135 à 137).</t>
+          <t>Conclusion établie sur les documents reçus (rapport du 23/10/2026, diapositives 136 à 138).</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 139, 142 et 153 à 155 ; compte rendu de l'entretien placements du 19/10/2026.</t>
+          <t>Rapport du 23/10/2026, diapositives 140, 143 et 154 à 156 ; compte rendu de l'entretien placements du 19/10/2026.</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -2686,7 +2686,7 @@
       <c r="E36" s="66" t="n"/>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 140 à 148 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_actif_mobilisation et 8_sensibilite_retraits.</t>
+          <t>Rapport du 23/10/2026, diapositives 141 à 149 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_actif_mobilisation et 8_sensibilite_retraits.</t>
         </is>
       </c>
       <c r="G36" s="23" t="n">
@@ -2738,7 +2738,7 @@
       <c r="E37" s="66" t="n"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Écoulement de l'épargne et écarts de liquidité année par année (rapport du 23/10/2026, diapositives 145 et 146). Encours des placements lus dans les grands livres (diapositive 153). Reste : inventaire et échéancier signés des placements. Items PBC attendus : 53, 54, 55.</t>
+          <t>Écoulement de l'épargne et écarts de liquidité année par année (rapport du 23/10/2026, diapositives 146 et 147). Encours des placements lus dans les grands livres (diapositive 154). Reste : inventaire et échéancier signés des placements. Items PBC attendus : 53, 54, 55.</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -2786,7 +2786,7 @@
       <c r="E38" s="66" t="n"/>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t>Encours moyen et rendement lus dans les grands livres (rapport du 23/10/2026, diapositives 153, 156 et 203) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 7_rendement_placements, 26_placements_gl et D9_placements_gl.</t>
+          <t>Encours moyen et rendement lus dans les grands livres (rapport du 23/10/2026, diapositives 154, 157 et 208) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 7_rendement_placements, 26_placements_gl et D9_placements_gl.</t>
         </is>
       </c>
       <c r="G38" s="23" t="n">
@@ -2834,7 +2834,7 @@
       <c r="E39" s="67" t="n"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Conclusions établies sur les documents reçus (rapport du 23/10/2026, diapositives 149 et 157).</t>
+          <t>Conclusions établies sur les documents reçus (rapport du 23/10/2026, diapositives 150 et 158).</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 159 à 179 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_ratios et 10_ratios_detail.</t>
+          <t>Rapport du 23/10/2026, diapositives 160 à 185, avec la définition et la lecture de chaque ratio ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_ratios et 10_ratios_detail.</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -2985,7 +2985,7 @@
       <c r="E42" s="66" t="n"/>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 180 à 188 (excédent par risque, ratios par garantie, affectation des excédents, marge de solvabilité, dispositif actuariel, plan comptable) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_controle_pcms, 10_marge_solvabilite, 10_affectation_excedents et 10_excedent_par_risque.</t>
+          <t>Rapport du 23/10/2026, diapositives 167, 168 et 186 à 193 (ratios par garantie, excédent par risque, affectation des excédents, marge de solvabilité, dispositif actuariel, plan comptable) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_controle_pcms, 10_marge_solvabilite, 10_affectation_excedents et 10_excedent_par_risque.</t>
         </is>
       </c>
       <c r="G42" s="23" t="n">
@@ -3033,7 +3033,7 @@
       <c r="E43" s="66" t="n"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 191 à 204 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 13a à 13i.</t>
+          <t>Rapport du 23/10/2026, diapositives 196 à 209 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 13a à 13i.</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -3085,7 +3085,7 @@
       <c r="E44" s="67" t="n"/>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositive 169 (données en attente). Items PBC attendus : 3, 28, 29, 30.</t>
+          <t>Rapport du 23/10/2026, diapositive 175 (données en attente). Items PBC attendus : 3, 28, 29, 30.</t>
         </is>
       </c>
       <c r="G44" s="23" t="n">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Hypothèses de la projection agrégée (rapport du 23/10/2026, diapositives 212 et 213) : tendances, inflation médicale (diapositive 201), rendements (diapositive 203).</t>
+          <t>Hypothèses de la projection agrégée (rapport du 23/10/2026, diapositives 217 et 218) : tendances, inflation médicale (diapositive 206), rendements (diapositive 208).</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -3236,7 +3236,7 @@
       <c r="E47" s="66" t="n"/>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>Projection agrégée en deux scénarios (rapport du 23/10/2026, diapositives 214 et 215). Reste : projection par garantie, qui dépend des phases 3 et 4.</t>
+          <t>Projection agrégée en deux scénarios (rapport du 23/10/2026, diapositives 219 et 220). Reste : projection par garantie, qui dépend des phases 3 et 4.</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
@@ -3284,7 +3284,7 @@
       <c r="E48" s="67" t="n"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Tests de résistance et sensibilités (rapport du 23/10/2026, diapositives 147 et 191 à 204), à étendre à la projection par garantie.</t>
+          <t>Tests de résistance et sensibilités (rapport du 23/10/2026, diapositives 148 et 196 à 209), à étendre à la projection par garantie.</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026 (FPPN_Rapport_actuariel_statistique_20261023.pptx, 276 diapositives) et classeur FPPN_Calculs_rapport_20261023.xlsx (onglet 9_tracabilite).</t>
+          <t>Rapport du 23/10/2026 (FPPN_Rapport_actuariel_statistique_20261023.pptx, 282 diapositives) et classeur FPPN_Calculs_rapport_20261023.xlsx (onglet 9_tracabilite).</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -3484,7 +3484,7 @@
       <c r="E52" s="66" t="n"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Contrôle automatique : 2 497 chiffres du rapport retrouvés dans les calculs. Vérification indépendante sur les fichiers du client (FPPN_Verification_coherence_20261023.xlsx, 15 anomalies corrigées). À refaire sur le rapport provisoire.</t>
+          <t>Contrôle automatique : 2 871 chiffres du rapport retrouvés dans les calculs. Vérification indépendante sur les fichiers du client (FPPN_Verification_coherence_20261023.xlsx, 18 anomalies corrigées). À refaire sur le rapport provisoire.</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">

--- a/FPPN_Plan_de_travail_Actuariat_20261023.xlsx
+++ b/FPPN_Plan_de_travail_Actuariat_20261023.xlsx
@@ -1357,7 +1357,7 @@
       <c r="E10" s="66" t="n"/>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 25 à 28 (cadre juridique, statuts et règlement intérieur, garanties et produits). Versions des statuts antérieures à 2023 non reçues. Item PBC attendu : 1.</t>
+          <t>Rapport du 23/10/2026, diapositives 29 à 32 (cadre juridique, statuts et règlement intérieur, garanties et produits). Versions des statuts antérieures à 2023 non reçues. Item PBC attendu : 1.</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -1461,7 +1461,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Tables retenues (rapport du 23/10/2026, diapositives 210 à 216). SMIG de 75 000 FCFA (décret n° 2022-986 du 21/12/2022) appliqué au plafond de l'indemnité de départ (diapositive 134). Rendements lus dans les grands livres (diapositive 154). Reste : âge de départ du personnel et hypothèses de projection (phase 7). Items PBC attendus : 13, 78.</t>
+          <t>Tables retenues (rapport du 23/10/2026, diapositives 218 à 224). SMIG de 75 000 FCFA (décret n° 2022-986 du 21/12/2022) appliqué au plafond de l'indemnité de départ (diapositive 142). Rendements lus dans les grands livres (diapositive 162). Reste : âge de départ du personnel et hypothèses de projection (phase 7). Items PBC attendus : 13, 78.</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Extraction FPPN_extraction_20261018_1939.zip : 4 287 fichiers, journal journal_fichiers.csv. Envois du 22/10/2026 inventoriés. Fichiers vides ou endommagés recensés (rapport du 23/10/2026, diapositive 45).</t>
+          <t>Extraction FPPN_extraction_20261018_1939.zip : 4 287 fichiers, journal journal_fichiers.csv. Envois du 22/10/2026 inventoriés. Fichiers vides ou endommagés recensés (rapport du 23/10/2026, diapositive 53).</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -1614,7 +1614,7 @@
       <c r="E15" s="66" t="n"/>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 38 à 46 (contrôles, qualité des bases variable par variable). Vérification indépendante des chiffres (FPPN_Verification_coherence_20261023.xlsx) : 506 feuilles de précomptes, 43 102 485 135 FCFA, 7 balances identiques.</t>
+          <t>Rapport du 23/10/2026, diapositives 46 à 54 (contrôles, qualité des bases variable par variable). Vérification indépendante des chiffres (FPPN_Verification_coherence_20261023.xlsx) : 506 feuilles de précomptes, 43 102 485 135 FCFA, 7 balances identiques.</t>
         </is>
       </c>
       <c r="G15" s="23" t="n">
@@ -1666,7 +1666,7 @@
       <c r="E16" s="66" t="n"/>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 43 et 44 (rapprochement aller et retour, écarts du PEP) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglet 1_aller_retour.</t>
+          <t>Rapport du 23/10/2026, diapositives 51 et 52 (rapprochement aller et retour, écarts du PEP) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglet 1_aller_retour. Circuits par produit d'après les logigrammes du FPPN, contrôles absents signalés (diapositives 35 à 38 ; FPPN_Logigrammes_cotisations_mis_a_jour_20261023.pptx).</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -1718,7 +1718,7 @@
       <c r="E17" s="66" t="n"/>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>Couverture mesurée de janvier 2020 à août 2026 (rapport du 23/10/2026, diapositive 40). Restent vides : fichiers maladie 936 et décès 8Z6 de décembre 2024. Fichier retour 9X4 de décembre 2024 manquant (diapositive 45). Items PBC attendus : 38, 39, 40.</t>
+          <t>Couverture mesurée de janvier 2020 à août 2026 (rapport du 23/10/2026, diapositive 48). Restent vides : fichiers maladie 936 et décès 8Z6 de décembre 2024. Fichier retour 9X4 de décembre 2024 manquant (diapositive 53). Items PBC attendus : 38, 39, 40.</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
@@ -1770,7 +1770,7 @@
       <c r="E18" s="66" t="n"/>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Cotisations comptabilisées et précomptées rapprochées (rapport du 23/10/2026, diapositive 60). Contrôles croisés états financiers, effectifs et rapprochements bancaires (diapositives 48 à 50). Reste : comptes individuels d'épargne. Items PBC attendus : 9.</t>
+          <t>Cotisations comptabilisées et précomptées rapprochées (rapport du 23/10/2026, diapositive 68). Contrôles croisés états financiers, effectifs et rapprochements bancaires (diapositives 56 à 58). Reste : comptes individuels d'épargne. Items PBC attendus : 9.</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -1822,7 +1822,7 @@
       <c r="E19" s="66" t="n"/>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>Aucune base de prestations extraite du logiciel. Le journal SIN et les états décès de fin d'année servent de base provisoire (rapport du 23/10/2026, diapositives 111 à 119). Items PBC attendus : 16, 47.</t>
+          <t>Aucune base de prestations extraite du logiciel. Le journal SIN et les états décès de fin d'année servent de base provisoire (rapport du 23/10/2026, diapositives 119 à 127). Items PBC attendus : 16, 47.</t>
         </is>
       </c>
       <c r="G19" s="23" t="n">
@@ -1874,7 +1874,7 @@
       <c r="E20" s="67" t="n"/>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Note sur les anomalies de données du 19/10/2026. Vérification de cohérence du 23/10/2026 (FPPN_Verification_coherence_20261023.xlsx, onglet 1_Anomalies). Questions au FPPN (rapport du 23/10/2026, diapositives 234 et 235). À tenir à jour à chaque envoi.</t>
+          <t>Note sur les anomalies de données du 19/10/2026. Vérification de cohérence du 23/10/2026 (FPPN_Verification_coherence_20261023.xlsx, onglet 1_Anomalies). Questions au FPPN (rapport du 23/10/2026, diapositives 243 et 244). À tenir à jour à chaque envoi.</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, partie 4 (diapositives 51 à 63). Limite : dates de naissance absentes des fichiers de précomptes (diapositive 46), fichier des ayants droit non reçu. Items PBC attendus : 4, 43.</t>
+          <t>Rapport du 23/10/2026, partie 4 (diapositives 59 à 71). Limite : dates de naissance absentes des fichiers de précomptes (diapositive 54), fichier des ayants droit non reçu. Items PBC attendus : 4, 43.</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
@@ -2030,7 +2030,7 @@
       <c r="E23" s="66" t="n"/>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, partie 5 (diapositives 64 à 78) et ratios par garantie (diapositive 167) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 3_, 12_sinistralite_variantes et 28_ratios_garantie.</t>
+          <t>Rapport du 23/10/2026, partie 5 (diapositives 72 à 86) et ratios par garantie (diapositive 175) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 3_, 12_sinistralite_variantes et 28_ratios_garantie.</t>
         </is>
       </c>
       <c r="G23" s="23" t="n">
@@ -2082,7 +2082,7 @@
       <c r="E24" s="66" t="n"/>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, parties 6 à 8 (diapositives 79 à 105) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 4_, 5_ et 6_.</t>
+          <t>Rapport du 23/10/2026, parties 6 à 8 (diapositives 87 à 113) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 4_, 5_ et 6_.</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -2130,7 +2130,7 @@
       <c r="E25" s="66" t="n"/>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>Méthodes retenues chiffrées sur les documents reçus : provision maladie, allocations décès, intérêts dus sur l'épargne, provision du personnel agent par agent (rapport du 23/10/2026, diapositives 90, 115, 119 et 123 à 134). Méthodes écartées en annexe (diapositives 237 à 244).</t>
+          <t>Méthodes retenues chiffrées sur les documents reçus : provision maladie, allocations décès, intérêts dus sur l'épargne, provision du personnel agent par agent (rapport du 23/10/2026, diapositives 98, 123, 127 et 131 à 142). Méthodes écartées en annexe (diapositives 246 à 253).</t>
         </is>
       </c>
       <c r="G25" s="23" t="n">
@@ -2178,7 +2178,7 @@
       <c r="E26" s="66" t="n"/>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Calculs par âge impossibles : dates de naissance absentes (rapport du 23/10/2026, diapositive 46). Analyses en attente et méthode retenue pour chacune (diapositive 233). Items PBC attendus : 4, 16, 43, 47.</t>
+          <t>Calculs par âge impossibles : dates de naissance absentes (rapport du 23/10/2026, diapositive 54). Analyses en attente et méthode retenue pour chacune (diapositive 242). Items PBC attendus : 4, 16, 43, 47.</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -2226,7 +2226,7 @@
       <c r="E27" s="67" t="n"/>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>Conclusion établie sur les documents reçus (rapport du 23/10/2026, diapositive 135). Les analyses en attente la préciseront sans en changer le sens (diapositive 233).</t>
+          <t>Conclusion établie sur les documents reçus (rapport du 23/10/2026, diapositive 143). Les analyses en attente la préciseront sans en changer le sens (diapositive 242).</t>
         </is>
       </c>
       <c r="G27" s="23" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 106 à 110 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 12_provisions_inventaire, 12_psap_rapprochement et 8_provisions_mois.</t>
+          <t>Rapport du 23/10/2026, diapositives 114 à 118 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 12_provisions_inventaire, 12_psap_rapprochement et 8_provisions_mois.</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -2382,7 +2382,7 @@
       <c r="E30" s="66" t="n"/>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t>Provision maladie mesurée sur les factures arrivées après la clôture et provision décès sur les dossiers connus (rapport du 23/10/2026, diapositives 111 à 120). Reste : base des prestations datée et liste des dossiers non payés. Items PBC attendus : 7, 47, 48, 64.</t>
+          <t>Provision maladie mesurée sur les factures arrivées après la clôture et provision décès sur les dossiers connus (rapport du 23/10/2026, diapositives 119 à 128). Reste : base des prestations datée et liste des dossiers non payés. Items PBC attendus : 7, 47, 48, 64.</t>
         </is>
       </c>
       <c r="G30" s="23" t="n">
@@ -2434,7 +2434,7 @@
       <c r="E31" s="66" t="n"/>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Provisions maladie et obsèques identiques depuis le 01/09/2020 : comparaison avec le recalcul (rapport du 23/10/2026, diapositive 137). Boni et mali par exercice en attente des bases avec dates de survenance et de paiement. Items PBC attendus : 16, 47.</t>
+          <t>Provisions maladie et obsèques identiques depuis le 01/09/2020 : comparaison avec le recalcul (rapport du 23/10/2026, diapositive 145). Boni et mali par exercice en attente des bases avec dates de survenance et de paiement. Items PBC attendus : 16, 47.</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -2486,7 +2486,7 @@
       <c r="E32" s="66" t="n"/>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 121 à 134 (Grenier, compte GNA, provision du personnel avec et sans plafond conventionnel) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 12_grenier_tranches, 12_gna_47111106, 14b_pidr_individuel et 27_pidr_plafond. Reste : note de calcul de la provision du personnel. Items PBC attendus : 51, 72, 78.</t>
+          <t>Rapport du 23/10/2026, diapositives 129 à 142 (Grenier, compte GNA, provision du personnel avec et sans plafond conventionnel) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 12_grenier_tranches, 12_gna_47111106, 14b_pidr_individuel et 27_pidr_plafond. Reste : note de calcul de la provision du personnel. Items PBC attendus : 51, 72, 78.</t>
         </is>
       </c>
       <c r="G32" s="23" t="n">
@@ -2534,7 +2534,7 @@
       <c r="E33" s="67" t="n"/>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Conclusion établie sur les documents reçus (rapport du 23/10/2026, diapositives 136 à 138).</t>
+          <t>Conclusion établie sur les documents reçus (rapport du 23/10/2026, diapositives 144 à 146).</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 140, 143 et 154 à 156 ; compte rendu de l'entretien placements du 19/10/2026.</t>
+          <t>Rapport du 23/10/2026, diapositives 148, 151 et 162 à 164 ; compte rendu de l'entretien placements du 19/10/2026.</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -2686,7 +2686,7 @@
       <c r="E36" s="66" t="n"/>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 141 à 149 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_actif_mobilisation et 8_sensibilite_retraits.</t>
+          <t>Rapport du 23/10/2026, diapositives 149 à 157 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_actif_mobilisation et 8_sensibilite_retraits.</t>
         </is>
       </c>
       <c r="G36" s="23" t="n">
@@ -2738,7 +2738,7 @@
       <c r="E37" s="66" t="n"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Écoulement de l'épargne et écarts de liquidité année par année (rapport du 23/10/2026, diapositives 146 et 147). Encours des placements lus dans les grands livres (diapositive 154). Reste : inventaire et échéancier signés des placements. Items PBC attendus : 53, 54, 55.</t>
+          <t>Écoulement de l'épargne et écarts de liquidité année par année (rapport du 23/10/2026, diapositives 154 et 155). Encours des placements lus dans les grands livres (diapositive 162). Reste : inventaire et échéancier signés des placements. Items PBC attendus : 53, 54, 55.</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -2786,7 +2786,7 @@
       <c r="E38" s="66" t="n"/>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t>Encours moyen et rendement lus dans les grands livres (rapport du 23/10/2026, diapositives 154, 157 et 208) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 7_rendement_placements, 26_placements_gl et D9_placements_gl.</t>
+          <t>Encours moyen et rendement lus dans les grands livres (rapport du 23/10/2026, diapositives 162, 165 et 216) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 7_rendement_placements, 26_placements_gl et D9_placements_gl.</t>
         </is>
       </c>
       <c r="G38" s="23" t="n">
@@ -2834,7 +2834,7 @@
       <c r="E39" s="67" t="n"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Conclusions établies sur les documents reçus (rapport du 23/10/2026, diapositives 150 et 158).</t>
+          <t>Conclusions établies sur les documents reçus (rapport du 23/10/2026, diapositives 158 et 166).</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 160 à 185, avec la définition et la lecture de chaque ratio ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_ratios et 10_ratios_detail.</t>
+          <t>Rapport du 23/10/2026, diapositives 168 à 193, avec la définition et la lecture de chaque ratio ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_ratios et 10_ratios_detail.</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -2985,7 +2985,7 @@
       <c r="E42" s="66" t="n"/>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 167, 168 et 186 à 193 (ratios par garantie, excédent par risque, affectation des excédents, marge de solvabilité, dispositif actuariel, plan comptable) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_controle_pcms, 10_marge_solvabilite, 10_affectation_excedents et 10_excedent_par_risque.</t>
+          <t>Rapport du 23/10/2026, diapositives 175, 176 et 194 à 201 (ratios par garantie, excédent par risque, affectation des excédents, marge de solvabilité, dispositif actuariel, plan comptable) ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 10_controle_pcms, 10_marge_solvabilite, 10_affectation_excedents et 10_excedent_par_risque.</t>
         </is>
       </c>
       <c r="G42" s="23" t="n">
@@ -3033,7 +3033,7 @@
       <c r="E43" s="66" t="n"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositives 196 à 209 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 13a à 13i.</t>
+          <t>Rapport du 23/10/2026, diapositives 204 à 217 ; classeur FPPN_Calculs_rapport_20261023.xlsx, onglets 13a à 13i.</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -3085,7 +3085,7 @@
       <c r="E44" s="67" t="n"/>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026, diapositive 175 (données en attente). Items PBC attendus : 3, 28, 29, 30.</t>
+          <t>Rapport du 23/10/2026, diapositive 183 (données en attente). Items PBC attendus : 3, 28, 29, 30.</t>
         </is>
       </c>
       <c r="G44" s="23" t="n">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Hypothèses de la projection agrégée (rapport du 23/10/2026, diapositives 217 et 218) : tendances, inflation médicale (diapositive 206), rendements (diapositive 208).</t>
+          <t>Hypothèses de la projection agrégée (rapport du 23/10/2026, diapositives 225 et 226) : tendances, inflation médicale (diapositive 214), rendements (diapositive 216).</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -3236,7 +3236,7 @@
       <c r="E47" s="66" t="n"/>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>Projection agrégée en deux scénarios (rapport du 23/10/2026, diapositives 219 et 220). Reste : projection par garantie, qui dépend des phases 3 et 4.</t>
+          <t>Projection agrégée en deux scénarios (rapport du 23/10/2026, diapositives 227 et 228). Reste : projection par garantie, qui dépend des phases 3 et 4.</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
@@ -3284,7 +3284,7 @@
       <c r="E48" s="67" t="n"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Tests de résistance et sensibilités (rapport du 23/10/2026, diapositives 148 et 196 à 209), à étendre à la projection par garantie.</t>
+          <t>Tests de résistance et sensibilités (rapport du 23/10/2026, diapositives 156 et 204 à 217), à étendre à la projection par garantie.</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Rapport du 23/10/2026 (FPPN_Rapport_actuariel_statistique_20261023.pptx, 282 diapositives) et classeur FPPN_Calculs_rapport_20261023.xlsx (onglet 9_tracabilite).</t>
+          <t>Rapport du 23/10/2026 (FPPN_Rapport_actuariel_statistique_20261023.pptx, 291 diapositives) et classeur FPPN_Calculs_rapport_20261023.xlsx (onglet 9_tracabilite).</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -3484,7 +3484,7 @@
       <c r="E52" s="66" t="n"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Contrôle automatique : 2 871 chiffres du rapport retrouvés dans les calculs. Vérification indépendante sur les fichiers du client (FPPN_Verification_coherence_20261023.xlsx, 18 anomalies corrigées). À refaire sur le rapport provisoire.</t>
+          <t>Contrôle automatique : 2 885 chiffres du rapport retrouvés dans les calculs. Vérification indépendante sur les fichiers du client (FPPN_Verification_coherence_20261023.xlsx, 18 anomalies corrigées). À refaire sur le rapport provisoire.</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">
